--- a/Project_ETF/ETF_Investment_Portfolio/00713/ETF_Investment_Portfolio_20261022.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/00713/ETF_Investment_Portfolio_20261022.xlsx
@@ -1063,17 +1063,17 @@
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>2207</t>
+          <t>4766</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>和泰車</t>
+          <t>南寶</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>2,360,000</t>
+          <t>3,521,000</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
@@ -1085,17 +1085,17 @@
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>4766</t>
+          <t>2207</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>南寶</t>
+          <t>和泰車</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>3,521,000</t>
+          <t>2,360,000</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
@@ -1217,17 +1217,17 @@
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>2206</t>
+          <t>2885</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>三陽工業</t>
+          <t>元大金</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>17,752,000</t>
+          <t>15,781,073</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
@@ -1239,17 +1239,17 @@
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>2885</t>
+          <t>2206</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>元大金</t>
+          <t>三陽工業</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>15,781,073</t>
+          <t>17,752,000</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
@@ -1371,17 +1371,17 @@
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>2376</t>
+          <t>9939</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>技嘉</t>
+          <t>宏全</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>2,943,000</t>
+          <t>8,119,597</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
@@ -1393,17 +1393,17 @@
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>9939</t>
+          <t>6670</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>宏全</t>
+          <t>復盛應用</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>8,119,597</t>
+          <t>3,881,000</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
@@ -1415,17 +1415,17 @@
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>6670</t>
+          <t>2376</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>復盛應用</t>
+          <t>技嘉</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>3,881,000</t>
+          <t>2,943,000</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
@@ -1525,17 +1525,17 @@
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>2882</t>
+          <t>4915</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>國泰金</t>
+          <t>致伸</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>7,718,000</t>
+          <t>14,131,000</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
@@ -1547,17 +1547,17 @@
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t>4915</t>
+          <t>2882</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>致伸</t>
+          <t>國泰金</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>14,131,000</t>
+          <t>7,718,000</t>
         </is>
       </c>
       <c r="D64" s="4" t="inlineStr">
